--- a/docs/deliverables/成果物一覧.xlsx
+++ b/docs/deliverables/成果物一覧.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="文書管理" sheetId="1" r:id="R6eef0509e8514cf1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="概要" sheetId="2" r:id="R7ddf50de3661407d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="文書管理" sheetId="1" r:id="R8ea2cb12ab1b4b9c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="概要" sheetId="2" r:id="Ra31cbc30b0224483"/>
   </x:sheets>
 </x:workbook>
 </file>
